--- a/DBs/nfl/Results/NFL_2017_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2017_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NFL_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nfl\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCCD83F3-4C2E-45DD-8D9D-E5CD8844C711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0789B945-DFCB-4BE7-9D3F-D38ABB027E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B484F9A8-15E8-4593-9F4F-5543AC5E83A0}"/>
   </bookViews>
@@ -118,9 +118,6 @@
     <t>WAS</t>
   </si>
   <si>
-    <t>STL</t>
-  </si>
-  <si>
     <t>IND</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>DEN</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
     <t>TB</t>
   </si>
   <si>
@@ -176,6 +170,12 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>LAR</t>
+  </si>
+  <si>
+    <t>LAC</t>
   </si>
 </sst>
 </file>
@@ -1645,10 +1645,10 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" t="s">
         <v>32</v>
-      </c>
-      <c r="F20" t="s">
-        <v>33</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1677,10 +1677,10 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
@@ -1709,10 +1709,10 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
         <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1741,10 +1741,10 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1773,10 +1773,10 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" t="s">
         <v>36</v>
-      </c>
-      <c r="F24" t="s">
-        <v>37</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
@@ -1805,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
@@ -1837,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" t="s">
         <v>38</v>
-      </c>
-      <c r="F26" t="s">
-        <v>39</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1869,10 +1869,10 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
@@ -1901,10 +1901,10 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" t="s">
         <v>40</v>
-      </c>
-      <c r="F28" t="s">
-        <v>41</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -1933,10 +1933,10 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
@@ -1965,10 +1965,10 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1997,10 +1997,10 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
@@ -2093,7 +2093,7 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -2128,7 +2128,7 @@
         <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
@@ -2157,7 +2157,7 @@
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
@@ -2192,7 +2192,7 @@
         <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
@@ -2288,7 +2288,7 @@
         <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
@@ -2317,7 +2317,7 @@
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -2480,7 +2480,7 @@
         <v>22</v>
       </c>
       <c r="F46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
@@ -2509,7 +2509,7 @@
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F47" t="s">
         <v>22</v>
@@ -2544,7 +2544,7 @@
         <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G48" t="s">
         <v>14</v>
@@ -2573,7 +2573,7 @@
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F49" t="s">
         <v>13</v>
@@ -2605,10 +2605,10 @@
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F50" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G50" t="s">
         <v>14</v>
@@ -2637,10 +2637,10 @@
         <v>11</v>
       </c>
       <c r="E51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F51" t="s">
         <v>43</v>
-      </c>
-      <c r="F51" t="s">
-        <v>45</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
@@ -2733,10 +2733,10 @@
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
@@ -2765,10 +2765,10 @@
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G55" t="s">
         <v>14</v>
@@ -2800,7 +2800,7 @@
         <v>31</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G56" t="s">
         <v>14</v>
@@ -2829,7 +2829,7 @@
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -2861,10 +2861,10 @@
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
@@ -2893,10 +2893,10 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G59" t="s">
         <v>14</v>
@@ -2928,7 +2928,7 @@
         <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
@@ -2957,7 +2957,7 @@
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -2992,7 +2992,7 @@
         <v>24</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G62" t="s">
         <v>14</v>
@@ -3021,7 +3021,7 @@
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F63" t="s">
         <v>24</v>
@@ -3053,10 +3053,10 @@
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G64" t="s">
         <v>14</v>
@@ -3085,10 +3085,10 @@
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F65" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
@@ -3184,7 +3184,7 @@
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
@@ -3213,7 +3213,7 @@
         <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
@@ -3312,7 +3312,7 @@
         <v>18</v>
       </c>
       <c r="F72" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
@@ -3341,7 +3341,7 @@
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F73" t="s">
         <v>18</v>
@@ -3373,10 +3373,10 @@
         <v>11</v>
       </c>
       <c r="E74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G74" t="s">
         <v>14</v>
@@ -3405,10 +3405,10 @@
         <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
@@ -3501,7 +3501,7 @@
         <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F78" t="s">
         <v>23</v>
@@ -3536,7 +3536,7 @@
         <v>23</v>
       </c>
       <c r="F79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G79" t="s">
         <v>14</v>
@@ -3629,10 +3629,10 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
@@ -3661,10 +3661,10 @@
         <v>11</v>
       </c>
       <c r="E83" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G83" t="s">
         <v>14</v>
@@ -3696,7 +3696,7 @@
         <v>30</v>
       </c>
       <c r="F84" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
@@ -3725,7 +3725,7 @@
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F85" t="s">
         <v>30</v>
@@ -3760,7 +3760,7 @@
         <v>29</v>
       </c>
       <c r="F86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
@@ -3789,7 +3789,7 @@
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F87" t="s">
         <v>29</v>
@@ -3821,7 +3821,7 @@
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F88" t="s">
         <v>21</v>
@@ -3856,7 +3856,7 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G89" t="s">
         <v>14</v>
@@ -3888,7 +3888,7 @@
         <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G90" t="s">
         <v>14</v>
@@ -3917,7 +3917,7 @@
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F91" t="s">
         <v>12</v>
@@ -4013,7 +4013,7 @@
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F94" t="s">
         <v>25</v>
@@ -4048,7 +4048,7 @@
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
@@ -4077,7 +4077,7 @@
         <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F96" t="s">
         <v>17</v>
@@ -4112,7 +4112,7 @@
         <v>17</v>
       </c>
       <c r="F97" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G97" t="s">
         <v>14</v>
@@ -4141,10 +4141,10 @@
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F98" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G98" t="s">
         <v>14</v>
@@ -4173,10 +4173,10 @@
         <v>11</v>
       </c>
       <c r="E99" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F99" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
@@ -4269,7 +4269,7 @@
         <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F102" t="s">
         <v>13</v>
@@ -4304,7 +4304,7 @@
         <v>13</v>
       </c>
       <c r="F103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
@@ -4397,10 +4397,10 @@
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G106" t="s">
         <v>14</v>
@@ -4429,10 +4429,10 @@
         <v>11</v>
       </c>
       <c r="E107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F107" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
@@ -4464,7 +4464,7 @@
         <v>24</v>
       </c>
       <c r="F108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G108" t="s">
         <v>14</v>
@@ -4493,7 +4493,7 @@
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F109" t="s">
         <v>24</v>
@@ -4720,7 +4720,7 @@
         <v>25</v>
       </c>
       <c r="F116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
@@ -4749,7 +4749,7 @@
         <v>11</v>
       </c>
       <c r="E117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F117" t="s">
         <v>25</v>
@@ -4781,10 +4781,10 @@
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F118" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
@@ -4813,10 +4813,10 @@
         <v>11</v>
       </c>
       <c r="E119" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F119" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G119" t="s">
         <v>14</v>
@@ -4848,7 +4848,7 @@
         <v>30</v>
       </c>
       <c r="F120" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G120" t="s">
         <v>14</v>
@@ -4877,7 +4877,7 @@
         <v>11</v>
       </c>
       <c r="E121" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F121" t="s">
         <v>30</v>
@@ -4909,7 +4909,7 @@
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -4944,7 +4944,7 @@
         <v>28</v>
       </c>
       <c r="F123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G123" t="s">
         <v>14</v>
@@ -4973,10 +4973,10 @@
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
@@ -5005,10 +5005,10 @@
         <v>11</v>
       </c>
       <c r="E125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F125" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G125" t="s">
         <v>14</v>
@@ -5104,7 +5104,7 @@
         <v>13</v>
       </c>
       <c r="F128" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G128" t="s">
         <v>14</v>
@@ -5133,7 +5133,7 @@
         <v>11</v>
       </c>
       <c r="E129" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F129" t="s">
         <v>13</v>
@@ -5165,7 +5165,7 @@
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F130" t="s">
         <v>29</v>
@@ -5200,7 +5200,7 @@
         <v>29</v>
       </c>
       <c r="F131" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G131" t="s">
         <v>14</v>
@@ -5293,7 +5293,7 @@
         <v>11</v>
       </c>
       <c r="E134" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F134" t="s">
         <v>24</v>
@@ -5328,7 +5328,7 @@
         <v>24</v>
       </c>
       <c r="F135" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G135" t="s">
         <v>15</v>
@@ -5421,10 +5421,10 @@
         <v>11</v>
       </c>
       <c r="E138" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F138" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
@@ -5453,10 +5453,10 @@
         <v>11</v>
       </c>
       <c r="E139" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F139" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G139" t="s">
         <v>14</v>
@@ -5613,10 +5613,10 @@
         <v>11</v>
       </c>
       <c r="E144" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F144" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G144" t="s">
         <v>14</v>
@@ -5645,10 +5645,10 @@
         <v>11</v>
       </c>
       <c r="E145" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F145" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
@@ -5741,10 +5741,10 @@
         <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F148" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G148" t="s">
         <v>14</v>
@@ -5773,10 +5773,10 @@
         <v>11</v>
       </c>
       <c r="E149" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
@@ -5805,10 +5805,10 @@
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G150" t="s">
         <v>14</v>
@@ -5837,10 +5837,10 @@
         <v>11</v>
       </c>
       <c r="E151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
@@ -5933,7 +5933,7 @@
         <v>11</v>
       </c>
       <c r="E154" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F154" t="s">
         <v>17</v>
@@ -5968,7 +5968,7 @@
         <v>17</v>
       </c>
       <c r="F155" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G155" t="s">
         <v>15</v>
@@ -6000,7 +6000,7 @@
         <v>30</v>
       </c>
       <c r="F156" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G156" t="s">
         <v>14</v>
@@ -6029,7 +6029,7 @@
         <v>11</v>
       </c>
       <c r="E157" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F157" t="s">
         <v>30</v>
@@ -6061,7 +6061,7 @@
         <v>11</v>
       </c>
       <c r="E158" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F158" t="s">
         <v>16</v>
@@ -6096,7 +6096,7 @@
         <v>16</v>
       </c>
       <c r="F159" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G159" t="s">
         <v>15</v>
@@ -6253,7 +6253,7 @@
         <v>11</v>
       </c>
       <c r="E164" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F164" t="s">
         <v>24</v>
@@ -6288,7 +6288,7 @@
         <v>24</v>
       </c>
       <c r="F165" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G165" t="s">
         <v>14</v>
@@ -6317,10 +6317,10 @@
         <v>11</v>
       </c>
       <c r="E166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F166" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G166" t="s">
         <v>15</v>
@@ -6349,10 +6349,10 @@
         <v>11</v>
       </c>
       <c r="E167" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F167" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G167" t="s">
         <v>14</v>
@@ -6448,7 +6448,7 @@
         <v>31</v>
       </c>
       <c r="F170" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G170" t="s">
         <v>15</v>
@@ -6477,7 +6477,7 @@
         <v>11</v>
       </c>
       <c r="E171" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F171" t="s">
         <v>31</v>
@@ -6512,7 +6512,7 @@
         <v>25</v>
       </c>
       <c r="F172" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G172" t="s">
         <v>15</v>
@@ -6541,7 +6541,7 @@
         <v>11</v>
       </c>
       <c r="E173" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F173" t="s">
         <v>25</v>
@@ -6573,7 +6573,7 @@
         <v>11</v>
       </c>
       <c r="E174" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F174" t="s">
         <v>26</v>
@@ -6608,7 +6608,7 @@
         <v>26</v>
       </c>
       <c r="F175" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G175" t="s">
         <v>15</v>
@@ -6701,7 +6701,7 @@
         <v>11</v>
       </c>
       <c r="E178" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -6736,7 +6736,7 @@
         <v>28</v>
       </c>
       <c r="F179" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G179" t="s">
         <v>15</v>
@@ -6765,10 +6765,10 @@
         <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F180" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G180" t="s">
         <v>14</v>
@@ -6797,10 +6797,10 @@
         <v>11</v>
       </c>
       <c r="E181" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F181" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G181" t="s">
         <v>15</v>
@@ -6832,7 +6832,7 @@
         <v>29</v>
       </c>
       <c r="F182" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G182" t="s">
         <v>15</v>
@@ -6861,7 +6861,7 @@
         <v>11</v>
       </c>
       <c r="E183" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F183" t="s">
         <v>29</v>
@@ -6960,7 +6960,7 @@
         <v>18</v>
       </c>
       <c r="F186" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G186" t="s">
         <v>15</v>
@@ -6989,7 +6989,7 @@
         <v>11</v>
       </c>
       <c r="E187" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F187" t="s">
         <v>18</v>
@@ -7021,7 +7021,7 @@
         <v>11</v>
       </c>
       <c r="E188" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F188" t="s">
         <v>19</v>
@@ -7056,7 +7056,7 @@
         <v>19</v>
       </c>
       <c r="F189" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G189" t="s">
         <v>14</v>
@@ -7088,7 +7088,7 @@
         <v>17</v>
       </c>
       <c r="F190" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G190" t="s">
         <v>15</v>
@@ -7117,7 +7117,7 @@
         <v>11</v>
       </c>
       <c r="E191" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F191" t="s">
         <v>17</v>
@@ -7216,7 +7216,7 @@
         <v>26</v>
       </c>
       <c r="F194" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G194" t="s">
         <v>14</v>
@@ -7245,7 +7245,7 @@
         <v>11</v>
       </c>
       <c r="E195" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F195" t="s">
         <v>26</v>
@@ -7277,7 +7277,7 @@
         <v>11</v>
       </c>
       <c r="E196" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F196" t="s">
         <v>25</v>
@@ -7312,7 +7312,7 @@
         <v>25</v>
       </c>
       <c r="F197" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G197" t="s">
         <v>14</v>
@@ -7341,10 +7341,10 @@
         <v>11</v>
       </c>
       <c r="E198" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F198" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G198" t="s">
         <v>14</v>
@@ -7373,10 +7373,10 @@
         <v>11</v>
       </c>
       <c r="E199" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F199" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G199" t="s">
         <v>15</v>
@@ -7405,7 +7405,7 @@
         <v>11</v>
       </c>
       <c r="E200" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F200" t="s">
         <v>20</v>
@@ -7440,7 +7440,7 @@
         <v>20</v>
       </c>
       <c r="F201" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G201" t="s">
         <v>14</v>
@@ -7469,10 +7469,10 @@
         <v>11</v>
       </c>
       <c r="E202" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F202" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G202" t="s">
         <v>14</v>
@@ -7501,10 +7501,10 @@
         <v>11</v>
       </c>
       <c r="E203" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F203" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G203" t="s">
         <v>15</v>
@@ -7597,10 +7597,10 @@
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F206" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G206" t="s">
         <v>15</v>
@@ -7629,10 +7629,10 @@
         <v>11</v>
       </c>
       <c r="E207" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F207" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G207" t="s">
         <v>14</v>
@@ -7661,10 +7661,10 @@
         <v>11</v>
       </c>
       <c r="E208" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F208" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G208" t="s">
         <v>14</v>
@@ -7693,10 +7693,10 @@
         <v>11</v>
       </c>
       <c r="E209" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F209" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G209" t="s">
         <v>15</v>
@@ -7856,7 +7856,7 @@
         <v>20</v>
       </c>
       <c r="F214" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G214" t="s">
         <v>15</v>
@@ -7885,7 +7885,7 @@
         <v>11</v>
       </c>
       <c r="E215" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F215" t="s">
         <v>20</v>
@@ -7917,7 +7917,7 @@
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F216" t="s">
         <v>23</v>
@@ -7952,7 +7952,7 @@
         <v>23</v>
       </c>
       <c r="F217" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G217" t="s">
         <v>15</v>
@@ -8112,7 +8112,7 @@
         <v>21</v>
       </c>
       <c r="F222" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G222" t="s">
         <v>15</v>
@@ -8141,7 +8141,7 @@
         <v>11</v>
       </c>
       <c r="E223" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F223" t="s">
         <v>21</v>
@@ -8173,10 +8173,10 @@
         <v>11</v>
       </c>
       <c r="E224" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F224" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G224" t="s">
         <v>14</v>
@@ -8205,10 +8205,10 @@
         <v>11</v>
       </c>
       <c r="E225" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F225" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G225" t="s">
         <v>15</v>
@@ -8237,7 +8237,7 @@
         <v>11</v>
       </c>
       <c r="E226" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F226" t="s">
         <v>17</v>
@@ -8272,7 +8272,7 @@
         <v>17</v>
       </c>
       <c r="F227" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G227" t="s">
         <v>14</v>
@@ -8304,7 +8304,7 @@
         <v>13</v>
       </c>
       <c r="F228" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G228" t="s">
         <v>15</v>
@@ -8333,7 +8333,7 @@
         <v>11</v>
       </c>
       <c r="E229" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F229" t="s">
         <v>13</v>
@@ -8368,7 +8368,7 @@
         <v>30</v>
       </c>
       <c r="F230" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G230" t="s">
         <v>15</v>
@@ -8397,7 +8397,7 @@
         <v>11</v>
       </c>
       <c r="E231" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F231" t="s">
         <v>30</v>
@@ -8429,7 +8429,7 @@
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F232" t="s">
         <v>27</v>
@@ -8464,7 +8464,7 @@
         <v>27</v>
       </c>
       <c r="F233" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G233" t="s">
         <v>14</v>
@@ -8493,7 +8493,7 @@
         <v>11</v>
       </c>
       <c r="E234" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F234" t="s">
         <v>31</v>
@@ -8528,7 +8528,7 @@
         <v>31</v>
       </c>
       <c r="F235" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G235" t="s">
         <v>15</v>
@@ -8624,7 +8624,7 @@
         <v>12</v>
       </c>
       <c r="F238" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G238" t="s">
         <v>15</v>
@@ -8653,7 +8653,7 @@
         <v>11</v>
       </c>
       <c r="E239" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F239" t="s">
         <v>12</v>
@@ -8749,7 +8749,7 @@
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F242" t="s">
         <v>16</v>
@@ -8784,7 +8784,7 @@
         <v>16</v>
       </c>
       <c r="F243" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G243" t="s">
         <v>14</v>
@@ -8880,7 +8880,7 @@
         <v>30</v>
       </c>
       <c r="F246" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G246" t="s">
         <v>15</v>
@@ -8909,7 +8909,7 @@
         <v>11</v>
       </c>
       <c r="E247" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F247" t="s">
         <v>30</v>
@@ -8941,10 +8941,10 @@
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F248" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G248" t="s">
         <v>15</v>
@@ -8973,10 +8973,10 @@
         <v>11</v>
       </c>
       <c r="E249" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F249" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G249" t="s">
         <v>14</v>
@@ -9005,10 +9005,10 @@
         <v>11</v>
       </c>
       <c r="E250" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F250" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G250" t="s">
         <v>14</v>
@@ -9037,10 +9037,10 @@
         <v>11</v>
       </c>
       <c r="E251" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F251" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G251" t="s">
         <v>15</v>
@@ -9133,7 +9133,7 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F254" t="s">
         <v>27</v>
@@ -9168,7 +9168,7 @@
         <v>27</v>
       </c>
       <c r="F255" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G255" t="s">
         <v>15</v>
@@ -9200,7 +9200,7 @@
         <v>25</v>
       </c>
       <c r="F256" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G256" t="s">
         <v>14</v>
@@ -9229,7 +9229,7 @@
         <v>11</v>
       </c>
       <c r="E257" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F257" t="s">
         <v>25</v>
@@ -9264,7 +9264,7 @@
         <v>31</v>
       </c>
       <c r="F258" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G258" t="s">
         <v>14</v>
@@ -9293,7 +9293,7 @@
         <v>11</v>
       </c>
       <c r="E259" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F259" t="s">
         <v>31</v>
@@ -9325,7 +9325,7 @@
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F260" t="s">
         <v>12</v>
@@ -9360,7 +9360,7 @@
         <v>12</v>
       </c>
       <c r="F261" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G261" t="s">
         <v>14</v>
@@ -9392,7 +9392,7 @@
         <v>28</v>
       </c>
       <c r="F262" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G262" t="s">
         <v>14</v>
@@ -9421,7 +9421,7 @@
         <v>11</v>
       </c>
       <c r="E263" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -9456,7 +9456,7 @@
         <v>24</v>
       </c>
       <c r="F264" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G264" t="s">
         <v>14</v>
@@ -9485,7 +9485,7 @@
         <v>11</v>
       </c>
       <c r="E265" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F265" t="s">
         <v>24</v>
@@ -9517,7 +9517,7 @@
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F266" t="s">
         <v>25</v>
@@ -9552,7 +9552,7 @@
         <v>25</v>
       </c>
       <c r="F267" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G267" t="s">
         <v>15</v>
@@ -9581,7 +9581,7 @@
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F268" t="s">
         <v>18</v>
@@ -9616,7 +9616,7 @@
         <v>18</v>
       </c>
       <c r="F269" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G269" t="s">
         <v>15</v>
@@ -9645,7 +9645,7 @@
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F270" t="s">
         <v>17</v>
@@ -9680,7 +9680,7 @@
         <v>17</v>
       </c>
       <c r="F271" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G271" t="s">
         <v>15</v>
@@ -9840,7 +9840,7 @@
         <v>26</v>
       </c>
       <c r="F276" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G276" t="s">
         <v>15</v>
@@ -9869,7 +9869,7 @@
         <v>11</v>
       </c>
       <c r="E277" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F277" t="s">
         <v>26</v>
@@ -9901,7 +9901,7 @@
         <v>11</v>
       </c>
       <c r="E278" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -9936,7 +9936,7 @@
         <v>31</v>
       </c>
       <c r="F279" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G279" t="s">
         <v>15</v>
@@ -9968,7 +9968,7 @@
         <v>22</v>
       </c>
       <c r="F280" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G280" t="s">
         <v>14</v>
@@ -9997,7 +9997,7 @@
         <v>11</v>
       </c>
       <c r="E281" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F281" t="s">
         <v>22</v>
@@ -10029,7 +10029,7 @@
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F282" t="s">
         <v>19</v>
@@ -10064,7 +10064,7 @@
         <v>19</v>
       </c>
       <c r="F283" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G283" t="s">
         <v>14</v>
@@ -10093,7 +10093,7 @@
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F284" t="s">
         <v>27</v>
@@ -10128,7 +10128,7 @@
         <v>27</v>
       </c>
       <c r="F285" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G285" t="s">
         <v>14</v>
@@ -10160,7 +10160,7 @@
         <v>16</v>
       </c>
       <c r="F286" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G286" t="s">
         <v>15</v>
@@ -10189,7 +10189,7 @@
         <v>11</v>
       </c>
       <c r="E287" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F287" t="s">
         <v>16</v>
@@ -10221,10 +10221,10 @@
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F288" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G288" t="s">
         <v>15</v>
@@ -10253,10 +10253,10 @@
         <v>11</v>
       </c>
       <c r="E289" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F289" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G289" t="s">
         <v>14</v>
@@ -10288,7 +10288,7 @@
         <v>13</v>
       </c>
       <c r="F290" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G290" t="s">
         <v>14</v>
@@ -10317,7 +10317,7 @@
         <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F291" t="s">
         <v>13</v>
@@ -10349,10 +10349,10 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F292" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G292" t="s">
         <v>15</v>
@@ -10381,10 +10381,10 @@
         <v>11</v>
       </c>
       <c r="E293" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F293" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G293" t="s">
         <v>14</v>
@@ -10672,7 +10672,7 @@
         <v>20</v>
       </c>
       <c r="F302" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G302" t="s">
         <v>14</v>
@@ -10701,7 +10701,7 @@
         <v>11</v>
       </c>
       <c r="E303" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F303" t="s">
         <v>20</v>
@@ -10733,7 +10733,7 @@
         <v>11</v>
       </c>
       <c r="E304" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F304" t="s">
         <v>12</v>
@@ -10768,7 +10768,7 @@
         <v>12</v>
       </c>
       <c r="F305" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G305" t="s">
         <v>14</v>
@@ -10797,10 +10797,10 @@
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F306" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G306" t="s">
         <v>14</v>
@@ -10829,10 +10829,10 @@
         <v>11</v>
       </c>
       <c r="E307" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F307" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G307" t="s">
         <v>15</v>
@@ -10861,10 +10861,10 @@
         <v>11</v>
       </c>
       <c r="E308" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F308" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G308" t="s">
         <v>15</v>
@@ -10893,10 +10893,10 @@
         <v>11</v>
       </c>
       <c r="E309" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F309" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G309" t="s">
         <v>14</v>
@@ -10925,7 +10925,7 @@
         <v>11</v>
       </c>
       <c r="E310" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F310" t="s">
         <v>31</v>
@@ -10960,7 +10960,7 @@
         <v>31</v>
       </c>
       <c r="F311" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G311" t="s">
         <v>14</v>
@@ -10989,7 +10989,7 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F312" t="s">
         <v>18</v>
@@ -11024,7 +11024,7 @@
         <v>18</v>
       </c>
       <c r="F313" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G313" t="s">
         <v>14</v>
@@ -11056,7 +11056,7 @@
         <v>21</v>
       </c>
       <c r="F314" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G314" t="s">
         <v>14</v>
@@ -11085,7 +11085,7 @@
         <v>11</v>
       </c>
       <c r="E315" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F315" t="s">
         <v>21</v>
@@ -11184,7 +11184,7 @@
         <v>30</v>
       </c>
       <c r="F318" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G318" t="s">
         <v>14</v>
@@ -11213,7 +11213,7 @@
         <v>11</v>
       </c>
       <c r="E319" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F319" t="s">
         <v>30</v>
@@ -11248,7 +11248,7 @@
         <v>16</v>
       </c>
       <c r="F320" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G320" t="s">
         <v>14</v>
@@ -11277,7 +11277,7 @@
         <v>11</v>
       </c>
       <c r="E321" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F321" t="s">
         <v>16</v>
@@ -11309,7 +11309,7 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F322" t="s">
         <v>24</v>
@@ -11344,7 +11344,7 @@
         <v>24</v>
       </c>
       <c r="F323" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G323" t="s">
         <v>15</v>
@@ -11373,10 +11373,10 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F324" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G324" t="s">
         <v>14</v>
@@ -11405,10 +11405,10 @@
         <v>11</v>
       </c>
       <c r="E325" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F325" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G325" t="s">
         <v>15</v>
@@ -11440,7 +11440,7 @@
         <v>31</v>
       </c>
       <c r="F326" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G326" t="s">
         <v>15</v>
@@ -11469,7 +11469,7 @@
         <v>11</v>
       </c>
       <c r="E327" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F327" t="s">
         <v>31</v>
@@ -11504,7 +11504,7 @@
         <v>16</v>
       </c>
       <c r="F328" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G328" t="s">
         <v>15</v>
@@ -11533,7 +11533,7 @@
         <v>11</v>
       </c>
       <c r="E329" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F329" t="s">
         <v>16</v>
@@ -11629,7 +11629,7 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F332" t="s">
         <v>19</v>
@@ -11664,7 +11664,7 @@
         <v>19</v>
       </c>
       <c r="F333" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G333" t="s">
         <v>15</v>
@@ -11824,7 +11824,7 @@
         <v>29</v>
       </c>
       <c r="F338" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G338" t="s">
         <v>14</v>
@@ -11853,7 +11853,7 @@
         <v>11</v>
       </c>
       <c r="E339" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F339" t="s">
         <v>29</v>
@@ -11888,7 +11888,7 @@
         <v>13</v>
       </c>
       <c r="F340" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G340" t="s">
         <v>15</v>
@@ -11917,7 +11917,7 @@
         <v>11</v>
       </c>
       <c r="E341" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F341" t="s">
         <v>13</v>
@@ -11949,10 +11949,10 @@
         <v>11</v>
       </c>
       <c r="E342" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F342" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G342" t="s">
         <v>14</v>
@@ -11981,10 +11981,10 @@
         <v>11</v>
       </c>
       <c r="E343" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F343" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G343" t="s">
         <v>15</v>
@@ -12080,7 +12080,7 @@
         <v>28</v>
       </c>
       <c r="F346" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G346" t="s">
         <v>15</v>
@@ -12109,7 +12109,7 @@
         <v>11</v>
       </c>
       <c r="E347" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -12141,10 +12141,10 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F348" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G348" t="s">
         <v>15</v>
@@ -12173,10 +12173,10 @@
         <v>11</v>
       </c>
       <c r="E349" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F349" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G349" t="s">
         <v>14</v>
@@ -12208,7 +12208,7 @@
         <v>22</v>
       </c>
       <c r="F350" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G350" t="s">
         <v>15</v>
@@ -12237,7 +12237,7 @@
         <v>11</v>
       </c>
       <c r="E351" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F351" t="s">
         <v>22</v>
@@ -12333,7 +12333,7 @@
         <v>11</v>
       </c>
       <c r="E354" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F354" t="s">
         <v>31</v>
@@ -12368,7 +12368,7 @@
         <v>31</v>
       </c>
       <c r="F355" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G355" t="s">
         <v>14</v>
@@ -12397,7 +12397,7 @@
         <v>11</v>
       </c>
       <c r="E356" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F356" t="s">
         <v>16</v>
@@ -12432,7 +12432,7 @@
         <v>16</v>
       </c>
       <c r="F357" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G357" t="s">
         <v>15</v>
@@ -12525,7 +12525,7 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F360" t="s">
         <v>17</v>
@@ -12560,7 +12560,7 @@
         <v>17</v>
       </c>
       <c r="F361" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G361" t="s">
         <v>15</v>
@@ -12592,7 +12592,7 @@
         <v>26</v>
       </c>
       <c r="F362" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G362" t="s">
         <v>15</v>
@@ -12621,7 +12621,7 @@
         <v>11</v>
       </c>
       <c r="E363" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F363" t="s">
         <v>26</v>
@@ -12653,10 +12653,10 @@
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F364" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G364" t="s">
         <v>15</v>
@@ -12685,10 +12685,10 @@
         <v>11</v>
       </c>
       <c r="E365" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F365" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G365" t="s">
         <v>14</v>
@@ -12781,10 +12781,10 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F368" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G368" t="s">
         <v>15</v>
@@ -12813,10 +12813,10 @@
         <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F369" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G369" t="s">
         <v>14</v>
@@ -12973,7 +12973,7 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F374" t="s">
         <v>23</v>
@@ -13008,7 +13008,7 @@
         <v>23</v>
       </c>
       <c r="F375" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G375" t="s">
         <v>14</v>
@@ -13037,10 +13037,10 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F376" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G376" t="s">
         <v>15</v>
@@ -13069,10 +13069,10 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F377" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G377" t="s">
         <v>14</v>
@@ -13101,7 +13101,7 @@
         <v>11</v>
       </c>
       <c r="E378" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F378" t="s">
         <v>25</v>
@@ -13136,7 +13136,7 @@
         <v>25</v>
       </c>
       <c r="F379" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G379" t="s">
         <v>15</v>
@@ -13168,7 +13168,7 @@
         <v>28</v>
       </c>
       <c r="F380" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G380" t="s">
         <v>15</v>
@@ -13197,7 +13197,7 @@
         <v>11</v>
       </c>
       <c r="E381" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F381" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F382" t="s">
         <v>30</v>
@@ -13264,7 +13264,7 @@
         <v>30</v>
       </c>
       <c r="F383" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G383" t="s">
         <v>14</v>
@@ -13360,7 +13360,7 @@
         <v>16</v>
       </c>
       <c r="F386" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G386" t="s">
         <v>15</v>
@@ -13389,7 +13389,7 @@
         <v>11</v>
       </c>
       <c r="E387" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F387" t="s">
         <v>16</v>
@@ -13424,7 +13424,7 @@
         <v>18</v>
       </c>
       <c r="F388" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G388" t="s">
         <v>15</v>
@@ -13453,7 +13453,7 @@
         <v>11</v>
       </c>
       <c r="E389" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F389" t="s">
         <v>18</v>
@@ -13485,10 +13485,10 @@
         <v>11</v>
       </c>
       <c r="E390" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F390" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G390" t="s">
         <v>15</v>
@@ -13517,10 +13517,10 @@
         <v>11</v>
       </c>
       <c r="E391" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F391" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G391" t="s">
         <v>14</v>
@@ -13613,7 +13613,7 @@
         <v>11</v>
       </c>
       <c r="E394" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F394" t="s">
         <v>23</v>
@@ -13648,7 +13648,7 @@
         <v>23</v>
       </c>
       <c r="F395" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G395" t="s">
         <v>15</v>
@@ -13677,10 +13677,10 @@
         <v>11</v>
       </c>
       <c r="E396" t="s">
+        <v>37</v>
+      </c>
+      <c r="F396" t="s">
         <v>38</v>
-      </c>
-      <c r="F396" t="s">
-        <v>39</v>
       </c>
       <c r="G396" t="s">
         <v>14</v>
@@ -13709,10 +13709,10 @@
         <v>11</v>
       </c>
       <c r="E397" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F397" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G397" t="s">
         <v>15</v>
@@ -13744,7 +13744,7 @@
         <v>24</v>
       </c>
       <c r="F398" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G398" t="s">
         <v>14</v>
@@ -13773,7 +13773,7 @@
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F399" t="s">
         <v>24</v>
@@ -13805,7 +13805,7 @@
         <v>11</v>
       </c>
       <c r="E400" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F400" t="s">
         <v>27</v>
@@ -13840,7 +13840,7 @@
         <v>27</v>
       </c>
       <c r="F401" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G401" t="s">
         <v>15</v>
@@ -13997,7 +13997,7 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F406" t="s">
         <v>19</v>
@@ -14032,7 +14032,7 @@
         <v>19</v>
       </c>
       <c r="F407" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G407" t="s">
         <v>14</v>
@@ -14061,7 +14061,7 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F408" t="s">
         <v>31</v>
@@ -14096,7 +14096,7 @@
         <v>31</v>
       </c>
       <c r="F409" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G409" t="s">
         <v>14</v>
@@ -14128,7 +14128,7 @@
         <v>26</v>
       </c>
       <c r="F410" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G410" t="s">
         <v>15</v>
@@ -14157,7 +14157,7 @@
         <v>11</v>
       </c>
       <c r="E411" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F411" t="s">
         <v>26</v>
@@ -14192,7 +14192,7 @@
         <v>30</v>
       </c>
       <c r="F412" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G412" t="s">
         <v>14</v>
@@ -14221,7 +14221,7 @@
         <v>11</v>
       </c>
       <c r="E413" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F413" t="s">
         <v>30</v>
@@ -14317,7 +14317,7 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F416" t="s">
         <v>13</v>
@@ -14352,7 +14352,7 @@
         <v>13</v>
       </c>
       <c r="F417" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G417" t="s">
         <v>14</v>
@@ -14381,10 +14381,10 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F418" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G418" t="s">
         <v>14</v>
@@ -14413,10 +14413,10 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F419" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G419" t="s">
         <v>15</v>
@@ -14512,7 +14512,7 @@
         <v>12</v>
       </c>
       <c r="F422" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G422" t="s">
         <v>15</v>
@@ -14541,7 +14541,7 @@
         <v>11</v>
       </c>
       <c r="E423" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F423" t="s">
         <v>12</v>
@@ -14576,7 +14576,7 @@
         <v>18</v>
       </c>
       <c r="F424" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G424" t="s">
         <v>15</v>
@@ -14605,7 +14605,7 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F425" t="s">
         <v>18</v>
@@ -14637,10 +14637,10 @@
         <v>11</v>
       </c>
       <c r="E426" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F426" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G426" t="s">
         <v>15</v>
@@ -14669,10 +14669,10 @@
         <v>11</v>
       </c>
       <c r="E427" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F427" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G427" t="s">
         <v>14</v>
@@ -14701,7 +14701,7 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F428" t="s">
         <v>21</v>
@@ -14736,7 +14736,7 @@
         <v>21</v>
       </c>
       <c r="F429" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G429" t="s">
         <v>14</v>
@@ -14957,7 +14957,7 @@
         <v>11</v>
       </c>
       <c r="E436" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F436" t="s">
         <v>19</v>
@@ -14992,7 +14992,7 @@
         <v>19</v>
       </c>
       <c r="F437" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G437" t="s">
         <v>14</v>
@@ -15024,7 +15024,7 @@
         <v>30</v>
       </c>
       <c r="F438" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G438" t="s">
         <v>14</v>
@@ -15053,7 +15053,7 @@
         <v>11</v>
       </c>
       <c r="E439" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F439" t="s">
         <v>30</v>
@@ -15085,10 +15085,10 @@
         <v>11</v>
       </c>
       <c r="E440" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F440" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G440" t="s">
         <v>14</v>
@@ -15117,10 +15117,10 @@
         <v>11</v>
       </c>
       <c r="E441" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F441" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G441" t="s">
         <v>15</v>
@@ -15213,7 +15213,7 @@
         <v>11</v>
       </c>
       <c r="E444" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F444" t="s">
         <v>29</v>
@@ -15248,7 +15248,7 @@
         <v>29</v>
       </c>
       <c r="F445" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G445" t="s">
         <v>14</v>
@@ -15277,7 +15277,7 @@
         <v>11</v>
       </c>
       <c r="E446" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F446" t="s">
         <v>28</v>
@@ -15312,7 +15312,7 @@
         <v>28</v>
       </c>
       <c r="F447" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G447" t="s">
         <v>15</v>
@@ -15344,7 +15344,7 @@
         <v>16</v>
       </c>
       <c r="F448" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G448" t="s">
         <v>14</v>
@@ -15373,7 +15373,7 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F449" t="s">
         <v>16</v>
@@ -15408,7 +15408,7 @@
         <v>20</v>
       </c>
       <c r="F450" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G450" t="s">
         <v>15</v>
@@ -15437,7 +15437,7 @@
         <v>11</v>
       </c>
       <c r="E451" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F451" t="s">
         <v>20</v>
@@ -15469,10 +15469,10 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F452" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G452" t="s">
         <v>14</v>
@@ -15501,10 +15501,10 @@
         <v>11</v>
       </c>
       <c r="E453" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F453" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G453" t="s">
         <v>15</v>
@@ -15533,7 +15533,7 @@
         <v>11</v>
       </c>
       <c r="E454" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F454" t="s">
         <v>16</v>
@@ -15568,7 +15568,7 @@
         <v>16</v>
       </c>
       <c r="F455" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G455" t="s">
         <v>14</v>
@@ -15661,10 +15661,10 @@
         <v>11</v>
       </c>
       <c r="E458" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F458" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G458" t="s">
         <v>15</v>
@@ -15693,10 +15693,10 @@
         <v>11</v>
       </c>
       <c r="E459" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F459" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G459" t="s">
         <v>14</v>
@@ -15856,7 +15856,7 @@
         <v>31</v>
       </c>
       <c r="F464" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G464" t="s">
         <v>15</v>
@@ -15885,7 +15885,7 @@
         <v>11</v>
       </c>
       <c r="E465" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>31</v>
@@ -15920,7 +15920,7 @@
         <v>12</v>
       </c>
       <c r="F466" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G466" t="s">
         <v>15</v>
@@ -15949,7 +15949,7 @@
         <v>11</v>
       </c>
       <c r="E467" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F467" t="s">
         <v>12</v>
@@ -15981,7 +15981,7 @@
         <v>11</v>
       </c>
       <c r="E468" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F468" t="s">
         <v>19</v>
@@ -16016,7 +16016,7 @@
         <v>19</v>
       </c>
       <c r="F469" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G469" t="s">
         <v>15</v>
@@ -16045,7 +16045,7 @@
         <v>11</v>
       </c>
       <c r="E470" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F470" t="s">
         <v>29</v>
@@ -16080,7 +16080,7 @@
         <v>29</v>
       </c>
       <c r="F471" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G471" t="s">
         <v>15</v>
@@ -16109,7 +16109,7 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F472" t="s">
         <v>26</v>
@@ -16144,7 +16144,7 @@
         <v>26</v>
       </c>
       <c r="F473" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G473" t="s">
         <v>14</v>
@@ -16176,7 +16176,7 @@
         <v>25</v>
       </c>
       <c r="F474" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G474" t="s">
         <v>15</v>
@@ -16205,7 +16205,7 @@
         <v>11</v>
       </c>
       <c r="E475" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F475" t="s">
         <v>25</v>
@@ -16237,10 +16237,10 @@
         <v>11</v>
       </c>
       <c r="E476" t="s">
+        <v>36</v>
+      </c>
+      <c r="F476" t="s">
         <v>37</v>
-      </c>
-      <c r="F476" t="s">
-        <v>38</v>
       </c>
       <c r="G476" t="s">
         <v>14</v>
@@ -16269,10 +16269,10 @@
         <v>11</v>
       </c>
       <c r="E477" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F477" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G477" t="s">
         <v>15</v>
@@ -16429,7 +16429,7 @@
         <v>11</v>
       </c>
       <c r="E482" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>17</v>
@@ -16464,7 +16464,7 @@
         <v>17</v>
       </c>
       <c r="F483" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G483" t="s">
         <v>14</v>
@@ -16557,7 +16557,7 @@
         <v>11</v>
       </c>
       <c r="E486" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F486" t="s">
         <v>27</v>
@@ -16592,7 +16592,7 @@
         <v>27</v>
       </c>
       <c r="F487" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G487" t="s">
         <v>14</v>
@@ -16621,7 +16621,7 @@
         <v>11</v>
       </c>
       <c r="E488" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F488" t="s">
         <v>30</v>
@@ -16656,7 +16656,7 @@
         <v>30</v>
       </c>
       <c r="F489" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G489" t="s">
         <v>15</v>
@@ -16688,7 +16688,7 @@
         <v>24</v>
       </c>
       <c r="F490" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G490" t="s">
         <v>15</v>
@@ -16717,7 +16717,7 @@
         <v>11</v>
       </c>
       <c r="E491" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>24</v>
@@ -16813,7 +16813,7 @@
         <v>11</v>
       </c>
       <c r="E494" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F494" t="s">
         <v>31</v>
@@ -16848,7 +16848,7 @@
         <v>31</v>
       </c>
       <c r="F495" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G495" t="s">
         <v>14</v>
@@ -16880,7 +16880,7 @@
         <v>16</v>
       </c>
       <c r="F496" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G496" t="s">
         <v>15</v>
@@ -16909,7 +16909,7 @@
         <v>11</v>
       </c>
       <c r="E497" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F497" t="s">
         <v>16</v>
@@ -16944,7 +16944,7 @@
         <v>18</v>
       </c>
       <c r="F498" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G498" t="s">
         <v>14</v>
@@ -16973,7 +16973,7 @@
         <v>11</v>
       </c>
       <c r="E499" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F499" t="s">
         <v>18</v>
@@ -17072,7 +17072,7 @@
         <v>25</v>
       </c>
       <c r="F502" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G502" t="s">
         <v>14</v>
@@ -17101,7 +17101,7 @@
         <v>11</v>
       </c>
       <c r="E503" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F503" t="s">
         <v>25</v>
@@ -17136,7 +17136,7 @@
         <v>12</v>
       </c>
       <c r="F504" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G504" t="s">
         <v>14</v>
@@ -17165,7 +17165,7 @@
         <v>11</v>
       </c>
       <c r="E505" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F505" t="s">
         <v>12</v>
@@ -17261,10 +17261,10 @@
         <v>11</v>
       </c>
       <c r="E508" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F508" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G508" t="s">
         <v>15</v>
@@ -17293,10 +17293,10 @@
         <v>11</v>
       </c>
       <c r="E509" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F509" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G509" t="s">
         <v>14</v>
@@ -17325,7 +17325,7 @@
         <v>11</v>
       </c>
       <c r="E510" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F510" t="s">
         <v>28</v>
@@ -17360,7 +17360,7 @@
         <v>28</v>
       </c>
       <c r="F511" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G511" t="s">
         <v>14</v>
@@ -17389,10 +17389,10 @@
         <v>11</v>
       </c>
       <c r="E512" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F512" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G512" t="s">
         <v>14</v>
@@ -17421,10 +17421,10 @@
         <v>11</v>
       </c>
       <c r="E513" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F513" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G513" t="s">
         <v>15</v>
@@ -17447,10 +17447,10 @@
         <v>2017</v>
       </c>
       <c r="C514" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D514" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E514" t="s">
         <v>29</v>
@@ -17479,10 +17479,10 @@
         <v>2017</v>
       </c>
       <c r="C515" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D515" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E515" t="s">
         <v>12</v>
@@ -17511,16 +17511,16 @@
         <v>2017</v>
       </c>
       <c r="C516" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D516" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E516" t="s">
         <v>16</v>
       </c>
       <c r="F516" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G516" t="s">
         <v>14</v>
@@ -17543,13 +17543,13 @@
         <v>2017</v>
       </c>
       <c r="C517" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D517" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E517" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F517" t="s">
         <v>16</v>
@@ -17575,10 +17575,10 @@
         <v>2017</v>
       </c>
       <c r="C518" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D518" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E518" t="s">
         <v>26</v>
@@ -17607,10 +17607,10 @@
         <v>2017</v>
       </c>
       <c r="C519" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D519" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E519" t="s">
         <v>18</v>
@@ -17639,16 +17639,16 @@
         <v>2017</v>
       </c>
       <c r="C520" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D520" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E520" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F520" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G520" t="s">
         <v>15</v>
@@ -17671,16 +17671,16 @@
         <v>2017</v>
       </c>
       <c r="C521" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D521" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E521" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F521" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G521" t="s">
         <v>14</v>
@@ -17703,10 +17703,10 @@
         <v>2017</v>
       </c>
       <c r="C522" t="s">
+        <v>44</v>
+      </c>
+      <c r="D522" t="s">
         <v>46</v>
-      </c>
-      <c r="D522" t="s">
-        <v>48</v>
       </c>
       <c r="E522" t="s">
         <v>30</v>
@@ -17735,10 +17735,10 @@
         <v>2017</v>
       </c>
       <c r="C523" t="s">
+        <v>44</v>
+      </c>
+      <c r="D523" t="s">
         <v>46</v>
-      </c>
-      <c r="D523" t="s">
-        <v>48</v>
       </c>
       <c r="E523" t="s">
         <v>16</v>
@@ -17767,10 +17767,10 @@
         <v>2017</v>
       </c>
       <c r="C524" t="s">
+        <v>44</v>
+      </c>
+      <c r="D524" t="s">
         <v>46</v>
-      </c>
-      <c r="D524" t="s">
-        <v>48</v>
       </c>
       <c r="E524" t="s">
         <v>13</v>
@@ -17799,10 +17799,10 @@
         <v>2017</v>
       </c>
       <c r="C525" t="s">
+        <v>44</v>
+      </c>
+      <c r="D525" t="s">
         <v>46</v>
-      </c>
-      <c r="D525" t="s">
-        <v>48</v>
       </c>
       <c r="E525" t="s">
         <v>29</v>
@@ -17831,10 +17831,10 @@
         <v>2017</v>
       </c>
       <c r="C526" t="s">
+        <v>44</v>
+      </c>
+      <c r="D526" t="s">
         <v>46</v>
-      </c>
-      <c r="D526" t="s">
-        <v>48</v>
       </c>
       <c r="E526" t="s">
         <v>26</v>
@@ -17863,10 +17863,10 @@
         <v>2017</v>
       </c>
       <c r="C527" t="s">
+        <v>44</v>
+      </c>
+      <c r="D527" t="s">
         <v>46</v>
-      </c>
-      <c r="D527" t="s">
-        <v>48</v>
       </c>
       <c r="E527" t="s">
         <v>22</v>
@@ -17895,16 +17895,16 @@
         <v>2017</v>
       </c>
       <c r="C528" t="s">
+        <v>44</v>
+      </c>
+      <c r="D528" t="s">
         <v>46</v>
       </c>
-      <c r="D528" t="s">
-        <v>48</v>
-      </c>
       <c r="E528" t="s">
+        <v>39</v>
+      </c>
+      <c r="F528" t="s">
         <v>40</v>
-      </c>
-      <c r="F528" t="s">
-        <v>41</v>
       </c>
       <c r="G528" t="s">
         <v>15</v>
@@ -17927,16 +17927,16 @@
         <v>2017</v>
       </c>
       <c r="C529" t="s">
+        <v>44</v>
+      </c>
+      <c r="D529" t="s">
         <v>46</v>
       </c>
-      <c r="D529" t="s">
-        <v>48</v>
-      </c>
       <c r="E529" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F529" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G529" t="s">
         <v>14</v>
@@ -17959,10 +17959,10 @@
         <v>2017</v>
       </c>
       <c r="C530" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D530" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E530" t="s">
         <v>13</v>
@@ -17991,10 +17991,10 @@
         <v>2017</v>
       </c>
       <c r="C531" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D531" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E531" t="s">
         <v>26</v>
@@ -18023,16 +18023,16 @@
         <v>2017</v>
       </c>
       <c r="C532" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D532" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E532" t="s">
         <v>30</v>
       </c>
       <c r="F532" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G532" t="s">
         <v>15</v>
@@ -18055,13 +18055,13 @@
         <v>2017</v>
       </c>
       <c r="C533" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D533" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E533" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F533" t="s">
         <v>30</v>
@@ -18087,10 +18087,10 @@
         <v>2017</v>
       </c>
       <c r="C534" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D534" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E534" t="s">
         <v>30</v>
@@ -18099,7 +18099,7 @@
         <v>13</v>
       </c>
       <c r="G534" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H534">
         <v>41</v>
@@ -18119,10 +18119,10 @@
         <v>2017</v>
       </c>
       <c r="C535" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D535" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E535" t="s">
         <v>13</v>
@@ -18131,7 +18131,7 @@
         <v>30</v>
       </c>
       <c r="G535" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H535">
         <v>33</v>
